--- a/example_data/scenarios.xlsx
+++ b/example_data/scenarios.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="scenario" sheetId="1" state="visible" r:id="rId3"/>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">alternative</t>
   </si>
   <si>
-    <t xml:space="preserve">Highprice</t>
+    <t xml:space="preserve">highprice</t>
   </si>
   <si>
     <t xml:space="preserve">lower_alternative</t>
@@ -130,12 +130,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -148,10 +148,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -579,7 +575,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="16.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="17.64"/>
   </cols>
